--- a/exports/UJJIVANSFB_full_report.xlsx
+++ b/exports/UJJIVANSFB_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>9.4</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="I2" t="n">
         <v>19.34795761677386</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-6.82</v>
+        <v>-10.59</v>
       </c>
       <c r="L2" t="n">
-        <v>7.53</v>
+        <v>10.82</v>
       </c>
       <c r="M2" t="n">
         <v>0.49</v>
       </c>
       <c r="N2" t="n">
-        <v>2.59</v>
+        <v>4.29</v>
       </c>
       <c r="O2" t="n">
         <v>-0.7</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.34</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44620.38541666666</v>
+        <v>44620.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>17.25</v>
+        <v>17.35</v>
       </c>
       <c r="I3" t="n">
         <v>17.27819622798942</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>9.210000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="L3" t="n">
         <v>5.79</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>12.54</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44645.55208333334</v>
+        <v>44648.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>16.1</v>
+        <v>15.75</v>
       </c>
       <c r="I4" t="n">
         <v>15.8140680226746</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>25</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.2</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>7.78</v>
+        <v>10.95</v>
       </c>
       <c r="M4" t="n">
         <v>2.03</v>
       </c>
       <c r="N4" t="n">
-        <v>2.59</v>
+        <v>3.11</v>
       </c>
       <c r="O4" t="n">
         <v>3.27</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>7.78</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44651.55208333334</v>
+        <v>44652.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>14.8</v>
+        <v>16.1</v>
       </c>
       <c r="I5" t="n">
         <v>15.99705581201116</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>6.03</v>
+        <v>-2.22</v>
       </c>
       <c r="L5" t="n">
-        <v>3.17</v>
+        <v>3.49</v>
       </c>
       <c r="M5" t="n">
         <v>1.33</v>
       </c>
       <c r="N5" t="n">
-        <v>0.33</v>
+        <v>10.81</v>
       </c>
       <c r="O5" t="n">
         <v>-3.11</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>12.34</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44691.38541666666</v>
+        <v>44691.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>17.1</v>
+        <v>16.55</v>
       </c>
       <c r="I6" t="n">
         <v>16.74858522386531</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K6" t="n">
-        <v>6.21</v>
+        <v>2.8</v>
       </c>
       <c r="L6" t="n">
         <v>8.07</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>10.17</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44694.38541666666</v>
+        <v>44694.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>17.4</v>
+        <v>17.65</v>
       </c>
       <c r="I7" t="n">
         <v>17.56769419249329</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.14</v>
+        <v>-6.65</v>
       </c>
       <c r="L7" t="n">
         <v>6.95</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>11.48</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44725.38541666666</v>
+        <v>44725.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="I8" t="n">
         <v>15.74869384008246</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>30.83333333333333</v>
+        <v>31</v>
       </c>
       <c r="K8" t="n">
-        <v>-10.48</v>
+        <v>-11.05</v>
       </c>
       <c r="L8" t="n">
-        <v>10.76</v>
+        <v>11.9</v>
       </c>
       <c r="M8" t="n">
         <v>2.16</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>6.08</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44743.38541666666</v>
+        <v>44743.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>14.9</v>
+        <v>15.35</v>
       </c>
       <c r="I9" t="n">
         <v>15.16858978198797</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>17.83333333333333</v>
+        <v>18</v>
       </c>
       <c r="K9" t="n">
-        <v>5.1</v>
+        <v>2.23</v>
       </c>
       <c r="L9" t="n">
         <v>0.96</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.34</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44827.55208333334</v>
+        <v>44830.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>23.45</v>
+        <v>22.2</v>
       </c>
       <c r="I10" t="n">
         <v>22.82177680827912</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>84</v>
+        <v>86.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>52.77</v>
+        <v>44.63</v>
       </c>
       <c r="L10" t="n">
         <v>3.26</v>
@@ -1011,7 +1130,7 @@
         <v>2.91</v>
       </c>
       <c r="N10" t="n">
-        <v>4.94</v>
+        <v>5.76</v>
       </c>
       <c r="O10" t="n">
         <v>1.66</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>13.19</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>23.4</v>
+        <v>24.15</v>
       </c>
       <c r="I11" t="n">
         <v>23.93088933184488</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.41</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>5.63</v>
+        <v>9.68</v>
       </c>
       <c r="M11" t="n">
         <v>1.83</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>11.5</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>30.3</v>
+        <v>29.2</v>
       </c>
       <c r="I12" t="n">
         <v>29.91801837403335</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>76</v>
+        <v>76.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>25.47</v>
+        <v>20.91</v>
       </c>
       <c r="L12" t="n">
         <v>4.14</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>11.87</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44925.55208333334</v>
+        <v>44928.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>29</v>
+        <v>29.8</v>
       </c>
       <c r="I13" t="n">
         <v>29.45220024543081</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>0.68</v>
+        <v>-2.05</v>
       </c>
       <c r="L13" t="n">
         <v>3.94</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.75</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44950.38541666666</v>
+        <v>44950.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>28.15</v>
+        <v>28</v>
       </c>
       <c r="I14" t="n">
         <v>28.09388214265786</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.54</v>
+        <v>-6.04</v>
       </c>
       <c r="L14" t="n">
         <v>6.88</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.970000000000001</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44960.55208333334</v>
+        <v>44963.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>29.45</v>
+        <v>30.1</v>
       </c>
       <c r="I15" t="n">
         <v>29.94095083357508</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.18</v>
+        <v>-7.5</v>
       </c>
       <c r="L15" t="n">
         <v>10.36</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>11</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44979.38541666666</v>
+        <v>44979.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>27</v>
+        <v>26.7</v>
       </c>
       <c r="I16" t="n">
         <v>26.78761783995639</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>-10.3</v>
+        <v>-11.3</v>
       </c>
       <c r="L16" t="n">
         <v>16.11</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.43</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45013.38541666666</v>
+        <v>45013.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>24.35</v>
+        <v>25</v>
       </c>
       <c r="I17" t="n">
         <v>24.88452904301771</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>33.83333333333334</v>
+        <v>34</v>
       </c>
       <c r="K17" t="n">
-        <v>8.800000000000001</v>
+        <v>6.37</v>
       </c>
       <c r="L17" t="n">
         <v>5.24</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45170.55208333334</v>
+        <v>45173.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>48.8</v>
+        <v>48.3</v>
       </c>
       <c r="I18" t="n">
         <v>48.34397883949527</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>157</v>
+        <v>159.8333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>95.2</v>
+        <v>93.2</v>
       </c>
       <c r="L18" t="n">
         <v>3</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>213</v>
+        <v>214</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>5.8</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45195.55208333334</v>
+        <v>45196.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>50.1</v>
+        <v>53.15</v>
       </c>
       <c r="I19" t="n">
         <v>50.59617906176548</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.73</v>
+        <v>-10.04</v>
       </c>
       <c r="L19" t="n">
-        <v>6.31</v>
+        <v>11.49</v>
       </c>
       <c r="M19" t="n">
         <v>1.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.28</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O19" t="n">
         <v>-0.92</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>8.42</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45222.38541666666</v>
+        <v>45222.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>54.4</v>
+        <v>53.8</v>
       </c>
       <c r="I20" t="n">
         <v>54.20961251962392</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>2.35</v>
+        <v>1.22</v>
       </c>
       <c r="L20" t="n">
         <v>5.64</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>8.720000000000001</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45236.38541666666</v>
+        <v>45236.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>55.8</v>
+        <v>58.3</v>
       </c>
       <c r="I21" t="n">
         <v>56.27990896398148</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.72</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>4.74</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M21" t="n">
         <v>1.66</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>11.14</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45251.55208333334</v>
+        <v>45252.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>55.5</v>
+        <v>54.3</v>
       </c>
       <c r="I22" t="n">
         <v>55.25971734502911</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.8</v>
+        <v>-6.86</v>
       </c>
       <c r="L22" t="n">
-        <v>5.4</v>
+        <v>7.03</v>
       </c>
       <c r="M22" t="n">
         <v>0.88</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>7.04</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45260.38541666666</v>
+        <v>45260.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>55.75</v>
+        <v>57.3</v>
       </c>
       <c r="I23" t="n">
         <v>56.79324870095466</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.67</v>
+        <v>-5.52</v>
       </c>
       <c r="L23" t="n">
-        <v>4.42</v>
+        <v>6.81</v>
       </c>
       <c r="M23" t="n">
         <v>0.09</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>7.16</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45279.55208333334</v>
+        <v>45280.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>59.6</v>
+        <v>57.5</v>
       </c>
       <c r="I24" t="n">
         <v>57.55807278461955</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>4.01</v>
+        <v>0.35</v>
       </c>
       <c r="L24" t="n">
         <v>3.4</v>
@@ -1809,7 +2096,7 @@
         <v>0.26</v>
       </c>
       <c r="N24" t="n">
-        <v>1.66</v>
+        <v>6.04</v>
       </c>
       <c r="O24" t="n">
         <v>5.14</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.26</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45301.55208333334</v>
+        <v>45302.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>57.75</v>
+        <v>59.35</v>
       </c>
       <c r="I25" t="n">
         <v>59.2729892790959</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.43</v>
+        <v>-3.22</v>
       </c>
       <c r="L25" t="n">
         <v>5.22</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>6.05</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45314.55208333334</v>
+        <v>45315.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I26" t="n">
         <v>57.33889414052294</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.27</v>
+        <v>-5.64</v>
       </c>
       <c r="L26" t="n">
-        <v>5.05</v>
+        <v>5.81</v>
       </c>
       <c r="M26" t="n">
         <v>0.83</v>
       </c>
       <c r="N26" t="n">
-        <v>1.84</v>
+        <v>4.48</v>
       </c>
       <c r="O26" t="n">
         <v>2.94</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>8.51</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45324.55208333334</v>
+        <v>45327.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>55.6</v>
+        <v>58.25</v>
       </c>
       <c r="I27" t="n">
         <v>58.05915584075716</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
-        <v>0.71</v>
+        <v>-4.02</v>
       </c>
       <c r="L27" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.55</v>
+        <v>2.79</v>
       </c>
       <c r="O27" t="n">
         <v>-4.48</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>7.88</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45331.55208333334</v>
+        <v>45334.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>57.4</v>
+        <v>55.05</v>
       </c>
       <c r="I28" t="n">
         <v>55.64509014292166</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.46</v>
+        <v>-5.49</v>
       </c>
       <c r="L28" t="n">
-        <v>5.06</v>
+        <v>6.01</v>
       </c>
       <c r="M28" t="n">
         <v>0.09</v>
       </c>
       <c r="N28" t="n">
-        <v>1.63</v>
+        <v>4.36</v>
       </c>
       <c r="O28" t="n">
         <v>2.79</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>11.34</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45383.38541666666</v>
+        <v>45383.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>47.55</v>
+        <v>48.4</v>
       </c>
       <c r="I29" t="n">
         <v>48.18565444770675</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K29" t="n">
-        <v>13.62</v>
+        <v>12.08</v>
       </c>
       <c r="L29" t="n">
         <v>4.81</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>9.83</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45421.38541666666</v>
+        <v>45421.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>52.75</v>
+        <v>51.9</v>
       </c>
       <c r="I30" t="n">
         <v>52.09985299267247</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>37.83333333333334</v>
+        <v>38</v>
       </c>
       <c r="K30" t="n">
-        <v>8.99</v>
+        <v>7.23</v>
       </c>
       <c r="L30" t="n">
         <v>2.27</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>6.88</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45524.55208333334</v>
+        <v>45525.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>43.51</v>
+        <v>43.69</v>
       </c>
       <c r="I31" t="n">
         <v>43.5271028557506</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>103</v>
+        <v>103.8333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>16.17</v>
+        <v>15.82</v>
       </c>
       <c r="L31" t="n">
         <v>5.39</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>6.17</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>43.13</v>
+        <v>42.42</v>
       </c>
       <c r="I32" t="n">
         <v>43.02890864009269</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.28</v>
+        <v>-2.91</v>
       </c>
       <c r="L32" t="n">
-        <v>1.88</v>
+        <v>3.36</v>
       </c>
       <c r="M32" t="n">
         <v>0.34</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>4.59</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45555.38541666666</v>
+        <v>45555.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>42.25</v>
+        <v>43.7</v>
       </c>
       <c r="I33" t="n">
         <v>43.62381643937485</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4</v>
+        <v>-3.02</v>
       </c>
       <c r="L33" t="n">
-        <v>2.19</v>
+        <v>3.25</v>
       </c>
       <c r="M33" t="n">
         <v>0.96</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.46</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45565.55208333334</v>
+        <v>45566.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>40.48</v>
+        <v>40.17</v>
       </c>
       <c r="I34" t="n">
         <v>40.44170665073759</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>-7.37</v>
+        <v>-8.08</v>
       </c>
       <c r="L34" t="n">
         <v>8.699999999999999</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>5.24</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45596.55208333334</v>
+        <v>45597.75</v>
       </c>
       <c r="H35" t="n">
-        <v>37.58</v>
+        <v>38.9</v>
       </c>
       <c r="I35" t="n">
         <v>38.14162971981561</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31.36458333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>6.45</v>
+        <v>3.16</v>
       </c>
       <c r="L35" t="n">
         <v>3.68</v>
       </c>
       <c r="M35" t="n">
-        <v>1.28</v>
+        <v>2.18</v>
       </c>
       <c r="N35" t="n">
-        <v>3.31</v>
+        <v>3.51</v>
       </c>
       <c r="O35" t="n">
         <v>-0.9399999999999999</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>8.42</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45604.55208333334</v>
+        <v>45607.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>37.31</v>
+        <v>35.95</v>
       </c>
       <c r="I36" t="n">
         <v>36.136784144689</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>6.802083333333333</v>
+        <v>9.635416666666666</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.09</v>
+        <v>-7.58</v>
       </c>
       <c r="L36" t="n">
-        <v>4.24</v>
+        <v>7.84</v>
       </c>
       <c r="M36" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="N36" t="n">
-        <v>2.46</v>
+        <v>4.07</v>
       </c>
       <c r="O36" t="n">
         <v>3.51</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.07</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45623.55208333334</v>
+        <v>45624.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>33.64</v>
+        <v>35.76</v>
       </c>
       <c r="I37" t="n">
         <v>34.08453758693365</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K37" t="n">
-        <v>6.43</v>
+        <v>0.53</v>
       </c>
       <c r="L37" t="n">
         <v>2.92</v>
@@ -2550,7 +2993,7 @@
         <v>1.45</v>
       </c>
       <c r="N37" t="n">
-        <v>1.82</v>
+        <v>6.84</v>
       </c>
       <c r="O37" t="n">
         <v>-4.07</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>9.43</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45644.55208333334</v>
+        <v>45645.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>35.15</v>
+        <v>34.68</v>
       </c>
       <c r="I38" t="n">
         <v>34.76216769799812</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.71</v>
+        <v>-3.02</v>
       </c>
       <c r="L38" t="n">
         <v>6.04</v>
       </c>
       <c r="M38" t="n">
-        <v>0.78</v>
+        <v>1.85</v>
       </c>
       <c r="N38" t="n">
         <v>3.03</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>4.53</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45665.38541666666</v>
+        <v>45665.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>35.03</v>
+        <v>35.46</v>
       </c>
       <c r="I39" t="n">
         <v>35.23538569627298</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.01</v>
+        <v>-2.25</v>
       </c>
       <c r="L39" t="n">
         <v>3.2</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>6.67</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45667.55208333334</v>
+        <v>45670.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>34.6</v>
+        <v>33.14</v>
       </c>
       <c r="I40" t="n">
         <v>33.56563779627807</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.43</v>
+        <v>-6.54</v>
       </c>
       <c r="L40" t="n">
-        <v>3.5</v>
+        <v>6.71</v>
       </c>
       <c r="M40" t="n">
-        <v>0.09</v>
+        <v>0.61</v>
       </c>
       <c r="N40" t="n">
-        <v>1.84</v>
+        <v>4.91</v>
       </c>
       <c r="O40" t="n">
         <v>3.53</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>9.92</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45686.55208333334</v>
+        <v>45687.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>34.4</v>
+        <v>35.35</v>
       </c>
       <c r="I41" t="n">
         <v>34.64900216759871</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.8</v>
+        <v>-6.67</v>
       </c>
       <c r="L41" t="n">
-        <v>6.37</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M41" t="n">
         <v>1.12</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>11.05</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>37.5</v>
+        <v>35.45</v>
       </c>
       <c r="I42" t="n">
         <v>36.71082481708155</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K42" t="n">
-        <v>6.08</v>
+        <v>0.28</v>
       </c>
       <c r="L42" t="n">
         <v>4.53</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>13.68</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45722.55208333334</v>
+        <v>45723.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>33.85</v>
+        <v>35.02</v>
       </c>
       <c r="I43" t="n">
         <v>33.9827084791733</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>4.51</v>
+        <v>1.21</v>
       </c>
       <c r="L43" t="n">
         <v>5.61</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>10.15</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45779.55208333334</v>
+        <v>45782.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>42.1</v>
+        <v>41.6</v>
       </c>
       <c r="I44" t="n">
         <v>41.71334257067529</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K44" t="n">
-        <v>20.22</v>
+        <v>18.79</v>
       </c>
       <c r="L44" t="n">
         <v>6.11</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>8.52</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45789.55208333334</v>
+        <v>45790.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>42.9</v>
+        <v>44</v>
       </c>
       <c r="I45" t="n">
         <v>43.72929880748305</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.12</v>
+        <v>-5.77</v>
       </c>
       <c r="L45" t="n">
-        <v>4.35</v>
+        <v>6.97</v>
       </c>
       <c r="M45" t="n">
         <v>4.31</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.52</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45842.55208333334</v>
+        <v>45845.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>48.35</v>
+        <v>47.12</v>
       </c>
       <c r="I46" t="n">
         <v>47.45271095767215</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K46" t="n">
-        <v>9.890000000000001</v>
+        <v>7.09</v>
       </c>
       <c r="L46" t="n">
         <v>3.32</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>9.73</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45908.55208333334</v>
+        <v>45909.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>44.16</v>
+        <v>47.05</v>
       </c>
       <c r="I47" t="n">
         <v>44.19004581893446</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K47" t="n">
-        <v>6.28</v>
+        <v>0.15</v>
       </c>
       <c r="L47" t="n">
         <v>6.71</v>
@@ -3120,7 +3683,7 @@
         <v>1.61</v>
       </c>
       <c r="N47" t="n">
-        <v>3.78</v>
+        <v>7.88</v>
       </c>
       <c r="O47" t="n">
         <v>-2.77</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>9.32</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45922.38541666666</v>
+        <v>45922.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>45.42</v>
+        <v>44.94</v>
       </c>
       <c r="I48" t="n">
         <v>45.10347892043664</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.46</v>
+        <v>-4.48</v>
       </c>
       <c r="L48" t="n">
         <v>5.8</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>5.26</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45930.55208333334</v>
+        <v>45931.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>46.2</v>
+        <v>47.79</v>
       </c>
       <c r="I49" t="n">
         <v>46.31902316304095</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.8</v>
+        <v>-6.34</v>
       </c>
       <c r="L49" t="n">
-        <v>3.49</v>
+        <v>6.74</v>
       </c>
       <c r="M49" t="n">
         <v>1.23</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.33</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45996.55208333334</v>
+        <v>45999.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>53.44</v>
+        <v>51.46</v>
       </c>
       <c r="I50" t="n">
         <v>52.73599225458724</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>65.16666666666667</v>
+        <v>68</v>
       </c>
       <c r="K50" t="n">
-        <v>11.82</v>
+        <v>7.68</v>
       </c>
       <c r="L50" t="n">
         <v>3.72</v>
@@ -3291,7 +3890,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="N50" t="n">
-        <v>2.59</v>
+        <v>3.54</v>
       </c>
       <c r="O50" t="n">
         <v>4.35</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>53.4</v>
+        <v>55.69</v>
       </c>
       <c r="I51" t="n">
         <v>54.32520490497787</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.77</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>7.07</v>
+        <v>9.09</v>
       </c>
       <c r="M51" t="n">
         <v>0.35</v>
       </c>
       <c r="N51" t="n">
-        <v>2.42</v>
+        <v>4.4</v>
       </c>
       <c r="O51" t="n">
         <v>-3.54</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.94</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46079.55208333334</v>
+        <v>46080.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>61.75</v>
+        <v>58.81</v>
       </c>
       <c r="I52" t="n">
         <v>59.34504717103131</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>55.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K52" t="n">
-        <v>10.88</v>
+        <v>5.6</v>
       </c>
       <c r="L52" t="n">
         <v>4.11</v>
@@ -3405,7 +4028,7 @@
         <v>1.62</v>
       </c>
       <c r="N52" t="n">
-        <v>4.1</v>
+        <v>6.45</v>
       </c>
       <c r="O52" t="n">
         <v>4.4</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>9.32</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46099.38541666666</v>
+        <v>46099.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>54.89</v>
+        <v>55.54</v>
       </c>
       <c r="I53" t="n">
         <v>55.3179177153794</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>6.67</v>
+        <v>5.56</v>
       </c>
       <c r="L53" t="n">
         <v>4.68</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>59.5</v>
+        <v>58.06</v>
       </c>
       <c r="I54" t="n">
         <v>58.95491622858376</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>54</v>
+        <v>54.83333333333334</v>
       </c>
       <c r="K54" t="n">
-        <v>7.13</v>
+        <v>4.54</v>
       </c>
       <c r="L54" t="n">
         <v>9.65</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>54.71</v>
+        <v>56.49</v>
       </c>
       <c r="I55" t="n">
         <v>55.78281894744678</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K55" t="n">
-        <v>5.77</v>
+        <v>2.7</v>
       </c>
       <c r="L55" t="n">
         <v>1.58</v>
       </c>
       <c r="M55" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="N55" t="n">
         <v>4.67</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.76</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46260.55208333334</v>
+        <v>46261.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>68.90000000000001</v>
+        <v>68.64</v>
       </c>
       <c r="I56" t="n">
         <v>68.75930868666744</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>72.16666666666667</v>
+        <v>73</v>
       </c>
       <c r="K56" t="n">
-        <v>21.97</v>
+        <v>21.51</v>
       </c>
       <c r="L56" t="n">
         <v>1.91</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>6.15</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46295.38541666666</v>
+        <v>46295.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>67.05</v>
+        <v>67.5</v>
       </c>
       <c r="I57" t="n">
         <v>67.16134310047151</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K57" t="n">
-        <v>2.32</v>
+        <v>1.66</v>
       </c>
       <c r="L57" t="n">
         <v>1.72</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>6.57</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46302.55208333334</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>65.14</v>
+        <v>61.95</v>
       </c>
       <c r="I58" t="n">
         <v>63.06464284698728</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.5</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>4.12</v>
+        <v>8.67</v>
       </c>
       <c r="M58" t="n">
         <v>0.76</v>
       </c>
       <c r="N58" t="n">
-        <v>2.86</v>
+        <v>4.36</v>
       </c>
       <c r="O58" t="n">
         <v>3.35</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3807,6 +4514,12 @@
       <c r="Q59" t="n">
         <v>26</v>
       </c>
+      <c r="R59" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5909,7 +6622,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.2</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="6">
@@ -5919,7 +6632,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="7">
@@ -5929,7 +6642,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>157</v>
+        <v>159.8</v>
       </c>
     </row>
     <row r="8">
@@ -5939,7 +6652,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -5949,7 +6662,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="10">
@@ -5959,7 +6672,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -5999,7 +6712,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.71</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="15">
@@ -6009,7 +6722,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.25</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="16">
@@ -6019,7 +6732,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.08</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="17">
@@ -6029,7 +6742,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>95.2</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="18">
@@ -6039,7 +6752,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.6</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="19">
@@ -6049,7 +6762,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.13</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="20">
@@ -6059,7 +6772,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.74</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="21">
@@ -6079,7 +6792,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -6089,7 +6802,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -6099,7 +6812,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="25">
@@ -6119,7 +6832,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.09</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="27">
@@ -6129,7 +6842,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.380000000000001</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="28">
@@ -6139,7 +6852,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
